--- a/PFP-C/Input data and Generated Schedule/142.xlsx
+++ b/PFP-C/Input data and Generated Schedule/142.xlsx
@@ -48664,7 +48664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48689,7 +48689,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -48699,7 +48699,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -48709,11 +48709,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>83.575</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -69955,7 +70075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69991,25 +70111,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -70042,18 +70157,15 @@
         <v>10.00000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>407.460960960961</v>
       </c>
       <c r="I2" t="n">
-        <v>407.460960960961</v>
+        <v>6.936936936936946</v>
       </c>
       <c r="J2" t="n">
-        <v>6.936936936936946</v>
-      </c>
-      <c r="K2" t="n">
         <v>1.702478912477109</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70086,18 +70198,15 @@
         <v>8.62842892768079</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>359.4587087087087</v>
       </c>
       <c r="I3" t="n">
-        <v>359.4587087087087</v>
+        <v>5.195195195195189</v>
       </c>
       <c r="J3" t="n">
-        <v>5.195195195195189</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.445282884884887</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70130,18 +70239,15 @@
         <v>8.75</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>387.0450450450452</v>
       </c>
       <c r="I4" t="n">
-        <v>387.0450450450452</v>
+        <v>5.990990990990991</v>
       </c>
       <c r="J4" t="n">
-        <v>5.990990990990991</v>
-      </c>
-      <c r="K4" t="n">
         <v>1.547879521437549</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70174,18 +70280,15 @@
         <v>7.20698254364088</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>372.9722222222222</v>
       </c>
       <c r="I5" t="n">
-        <v>372.9722222222222</v>
+        <v>4.339339339339328</v>
       </c>
       <c r="J5" t="n">
-        <v>4.339339339339328</v>
-      </c>
-      <c r="K5" t="n">
         <v>1.163448396635256</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70218,18 +70321,15 @@
         <v>6.942148760330573</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>319.8475975975976</v>
       </c>
       <c r="I6" t="n">
-        <v>319.8475975975976</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="J6" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="K6" t="n">
         <v>1.18299584308405</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70262,18 +70362,15 @@
         <v>8.4</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>295.533033033033</v>
       </c>
       <c r="I7" t="n">
-        <v>295.533033033033</v>
+        <v>4.414414414414415</v>
       </c>
       <c r="J7" t="n">
-        <v>4.414414414414415</v>
-      </c>
-      <c r="K7" t="n">
         <v>1.493712688936873</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70306,18 +70403,15 @@
         <v>5.600000000000005</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>432.9579579579579</v>
       </c>
       <c r="I8" t="n">
-        <v>432.9579579579579</v>
+        <v>4.204204204204207</v>
       </c>
       <c r="J8" t="n">
-        <v>4.204204204204207</v>
-      </c>
-      <c r="K8" t="n">
         <v>0.9710421362927004</v>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70350,18 +70444,15 @@
         <v>6.916426512968293</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>296.7364864864865</v>
       </c>
       <c r="I9" t="n">
-        <v>296.7364864864865</v>
+        <v>3.6036036036036</v>
       </c>
       <c r="J9" t="n">
-        <v>3.6036036036036</v>
-      </c>
-      <c r="K9" t="n">
         <v>1.214412034823264</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70394,18 +70485,15 @@
         <v>9.999999999999991</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>406.5645645645645</v>
       </c>
       <c r="I10" t="n">
-        <v>406.5645645645645</v>
+        <v>6.846846846846839</v>
       </c>
       <c r="J10" t="n">
-        <v>6.846846846846839</v>
-      </c>
-      <c r="K10" t="n">
         <v>1.684073685610032</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70438,18 +70526,15 @@
         <v>7.640692640692635</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>411.3648648648648</v>
       </c>
       <c r="I11" t="n">
-        <v>411.3648648648648</v>
+        <v>5.300300300300296</v>
       </c>
       <c r="J11" t="n">
-        <v>5.300300300300296</v>
-      </c>
-      <c r="K11" t="n">
         <v>1.288466943340304</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70482,18 +70567,15 @@
         <v>1.779935275080897</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>259.8280780780781</v>
       </c>
       <c r="I12" t="n">
-        <v>259.8280780780781</v>
+        <v>0.8258258258258214</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8258258258258214</v>
-      </c>
-      <c r="K12" t="n">
         <v>0.3178354825753903</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70526,18 +70608,15 @@
         <v>8.169934640522875</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>261.9324324324323</v>
       </c>
       <c r="I13" t="n">
-        <v>261.9324324324323</v>
+        <v>3.753753753753753</v>
       </c>
       <c r="J13" t="n">
-        <v>3.753753753753753</v>
-      </c>
-      <c r="K13" t="n">
         <v>1.433100024649321</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70570,18 +70649,15 @@
         <v>6.74351585014408</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>304.243993993994</v>
       </c>
       <c r="I14" t="n">
-        <v>304.243993993994</v>
+        <v>3.513513513513506</v>
       </c>
       <c r="J14" t="n">
-        <v>3.513513513513506</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.154834140647939</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70614,18 +70690,15 @@
         <v>6.05263157894735</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>362.1486486486486</v>
       </c>
       <c r="I15" t="n">
-        <v>362.1486486486486</v>
+        <v>3.798798798798787</v>
       </c>
       <c r="J15" t="n">
-        <v>3.798798798798787</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.048961196727901</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -70658,18 +70731,15 @@
         <v>6.493506493506499</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>265.5345345345345</v>
       </c>
       <c r="I16" t="n">
-        <v>265.5345345345345</v>
+        <v>3.003003003003005</v>
       </c>
       <c r="J16" t="n">
-        <v>3.003003003003005</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.130927473621118</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70702,18 +70772,15 @@
         <v>8.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>307.545045045045</v>
       </c>
       <c r="I17" t="n">
-        <v>307.545045045045</v>
+        <v>4.414414414414415</v>
       </c>
       <c r="J17" t="n">
-        <v>4.414414414414415</v>
-      </c>
-      <c r="K17" t="n">
         <v>1.435371658733065</v>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70746,18 +70813,15 @@
         <v>5.910224438902735</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>363.6629129129129</v>
       </c>
       <c r="I18" t="n">
-        <v>363.6629129129129</v>
+        <v>3.558558558558553</v>
       </c>
       <c r="J18" t="n">
-        <v>3.558558558558553</v>
-      </c>
-      <c r="K18" t="n">
         <v>0.9785321604710151</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70790,18 +70854,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>321.9617117117117</v>
       </c>
       <c r="I19" t="n">
-        <v>321.9617117117117</v>
+        <v>5.210210210210203</v>
       </c>
       <c r="J19" t="n">
-        <v>5.210210210210203</v>
-      </c>
-      <c r="K19" t="n">
         <v>1.618270129858014</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70834,18 +70895,15 @@
         <v>2.07171314741036</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>200.7124624624624</v>
       </c>
       <c r="I20" t="n">
-        <v>200.7124624624624</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K20" t="n">
         <v>0.3890046343917505</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -70878,18 +70936,15 @@
         <v>3.640897755610959</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>355.2545045045045</v>
       </c>
       <c r="I21" t="n">
-        <v>355.2545045045045</v>
+        <v>2.192192192192184</v>
       </c>
       <c r="J21" t="n">
-        <v>2.192192192192184</v>
-      </c>
-      <c r="K21" t="n">
         <v>0.6170765365100072</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -70922,18 +70977,15 @@
         <v>1.850649350649348</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>254.1231231231232</v>
       </c>
       <c r="I22" t="n">
-        <v>254.1231231231232</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K22" t="n">
         <v>0.3367878709097995</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -70966,18 +71018,15 @@
         <v>7.171428571428569</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>294.3318318318318</v>
       </c>
       <c r="I23" t="n">
-        <v>294.3318318318318</v>
+        <v>3.768768768768767</v>
       </c>
       <c r="J23" t="n">
-        <v>3.768768768768767</v>
-      </c>
-      <c r="K23" t="n">
         <v>1.280448922331335</v>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71010,18 +71059,15 @@
         <v>2.244094488188974</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>218.7282282282283</v>
       </c>
       <c r="I24" t="n">
-        <v>218.7282282282283</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.3912873353332458</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71054,18 +71100,15 @@
         <v>9.999999999999984</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>359.1584084084085</v>
       </c>
       <c r="I25" t="n">
-        <v>359.1584084084085</v>
+        <v>6.021021021021011</v>
       </c>
       <c r="J25" t="n">
-        <v>6.021021021021011</v>
-      </c>
-      <c r="K25" t="n">
         <v>1.67642490891494</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71098,18 +71141,15 @@
         <v>9.999999999999991</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>408.0660660660661</v>
       </c>
       <c r="I26" t="n">
-        <v>408.0660660660661</v>
+        <v>6.846846846846839</v>
       </c>
       <c r="J26" t="n">
-        <v>6.846846846846839</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.677877043992757</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71142,18 +71182,15 @@
         <v>4.314285714285709</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>307.8453453453453</v>
       </c>
       <c r="I27" t="n">
-        <v>307.8453453453453</v>
+        <v>2.267267267267264</v>
       </c>
       <c r="J27" t="n">
-        <v>2.267267267267264</v>
-      </c>
-      <c r="K27" t="n">
         <v>0.7364955493232523</v>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71186,18 +71223,15 @@
         <v>8.155339805825236</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>282.0503003003003</v>
       </c>
       <c r="I28" t="n">
-        <v>282.0503003003003</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="J28" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="K28" t="n">
         <v>1.341528011051634</v>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71230,18 +71264,15 @@
         <v>3.529411764705885</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>253.524024024024</v>
       </c>
       <c r="I29" t="n">
-        <v>253.524024024024</v>
+        <v>1.621621621621623</v>
       </c>
       <c r="J29" t="n">
-        <v>1.621621621621623</v>
-      </c>
-      <c r="K29" t="n">
         <v>0.639632329860762</v>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71274,18 +71305,15 @@
         <v>8.429752066115679</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>328.5563063063063</v>
       </c>
       <c r="I30" t="n">
-        <v>328.5563063063063</v>
+        <v>4.594594594594581</v>
       </c>
       <c r="J30" t="n">
-        <v>4.594594594594581</v>
-      </c>
-      <c r="K30" t="n">
         <v>1.398419237861511</v>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71318,18 +71346,15 @@
         <v>2.244094488188974</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>209.418918918919</v>
       </c>
       <c r="I31" t="n">
-        <v>209.418918918919</v>
+        <v>0.8558558558558549</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8558558558558549</v>
-      </c>
-      <c r="K31" t="n">
         <v>0.4086812501344341</v>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71362,18 +71387,15 @@
         <v>8.62842892768079</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>342.3415915915916</v>
       </c>
       <c r="I32" t="n">
-        <v>342.3415915915916</v>
+        <v>5.195195195195189</v>
       </c>
       <c r="J32" t="n">
-        <v>5.195195195195189</v>
-      </c>
-      <c r="K32" t="n">
         <v>1.51754718760348</v>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71406,18 +71428,15 @@
         <v>5.850144092219016</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>301.240990990991</v>
       </c>
       <c r="I33" t="n">
-        <v>301.240990990991</v>
+        <v>3.048048048048046</v>
       </c>
       <c r="J33" t="n">
-        <v>3.048048048048046</v>
-      </c>
-      <c r="K33" t="n">
         <v>1.011830441143118</v>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71450,18 +71469,15 @@
         <v>1.315789473684204</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>357.9444444444446</v>
       </c>
       <c r="I34" t="n">
-        <v>357.9444444444446</v>
+        <v>0.8258258258258214</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8258258258258214</v>
-      </c>
-      <c r="K34" t="n">
         <v>0.2307134078048235</v>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71494,18 +71510,15 @@
         <v>8.41498559077808</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>310.8506006006005</v>
       </c>
       <c r="I35" t="n">
-        <v>310.8506006006005</v>
+        <v>4.384384384384375</v>
       </c>
       <c r="J35" t="n">
-        <v>4.384384384384375</v>
-      </c>
-      <c r="K35" t="n">
         <v>1.410447454794432</v>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71538,18 +71551,15 @@
         <v>8.567493112947657</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>319.8475975975976</v>
       </c>
       <c r="I36" t="n">
-        <v>319.8475975975976</v>
+        <v>4.669669669669668</v>
       </c>
       <c r="J36" t="n">
-        <v>4.669669669669668</v>
-      </c>
-      <c r="K36" t="n">
         <v>1.459967092060079</v>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71582,18 +71592,15 @@
         <v>2.639593908629444</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>168.3205705705706</v>
       </c>
       <c r="I37" t="n">
-        <v>168.3205705705706</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J37" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K37" t="n">
         <v>0.4638653363246704</v>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71626,18 +71633,15 @@
         <v>9.999999999999991</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>292.5608108108108</v>
       </c>
       <c r="I38" t="n">
-        <v>292.5608108108108</v>
+        <v>4.639639639639635</v>
       </c>
       <c r="J38" t="n">
-        <v>4.639639639639635</v>
-      </c>
-      <c r="K38" t="n">
         <v>1.585871883107384</v>
       </c>
-      <c r="L38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71670,18 +71674,15 @@
         <v>3.085714285714289</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>286.8243243243243</v>
       </c>
       <c r="I39" t="n">
-        <v>286.8243243243243</v>
+        <v>1.621621621621623</v>
       </c>
       <c r="J39" t="n">
-        <v>1.621621621621623</v>
-      </c>
-      <c r="K39" t="n">
         <v>0.5653710247349828</v>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71714,18 +71715,15 @@
         <v>1.485714285714287</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>288.6261261261261</v>
       </c>
       <c r="I40" t="n">
-        <v>288.6261261261261</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J40" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K40" t="n">
         <v>0.2705163220184681</v>
       </c>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71758,18 +71756,15 @@
         <v>1.40049140049141</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>342.9376876876877</v>
       </c>
       <c r="I41" t="n">
-        <v>342.9376876876877</v>
+        <v>0.8558558558558615</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8558558558558615</v>
-      </c>
-      <c r="K41" t="n">
         <v>0.2495659959762973</v>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -71802,18 +71797,15 @@
         <v>8.155339805825236</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>281.1493993993994</v>
       </c>
       <c r="I42" t="n">
-        <v>281.1493993993994</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="J42" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="K42" t="n">
         <v>1.345826735488969</v>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -71846,18 +71838,15 @@
         <v>3.496732026143783</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>274.5450450450451</v>
       </c>
       <c r="I43" t="n">
-        <v>274.5450450450451</v>
+        <v>1.606606606606603</v>
       </c>
       <c r="J43" t="n">
-        <v>1.606606606606603</v>
-      </c>
-      <c r="K43" t="n">
         <v>0.5851887096862389</v>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71890,18 +71879,15 @@
         <v>2.07171314741036</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>212.7244744744744</v>
       </c>
       <c r="I44" t="n">
-        <v>212.7244744744744</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="J44" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="K44" t="n">
         <v>0.3670385284578386</v>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -71934,18 +71920,15 @@
         <v>8.793859649122805</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>386.7447447447447</v>
       </c>
       <c r="I45" t="n">
-        <v>386.7447447447447</v>
+        <v>6.021021021021017</v>
       </c>
       <c r="J45" t="n">
-        <v>6.021021021021017</v>
-      </c>
-      <c r="K45" t="n">
         <v>1.556846241051045</v>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -71978,18 +71961,15 @@
         <v>5.357142857142859</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>270.6396396396397</v>
       </c>
       <c r="I46" t="n">
-        <v>270.6396396396397</v>
+        <v>2.477477477477478</v>
       </c>
       <c r="J46" t="n">
-        <v>2.477477477477478</v>
-      </c>
-      <c r="K46" t="n">
         <v>0.9154155986818017</v>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -72022,18 +72002,15 @@
         <v>8.793859649122805</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>389.7477477477478</v>
       </c>
       <c r="I47" t="n">
-        <v>389.7477477477478</v>
+        <v>6.021021021021017</v>
       </c>
       <c r="J47" t="n">
-        <v>6.021021021021017</v>
-      </c>
-      <c r="K47" t="n">
         <v>1.544850754318646</v>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -72066,18 +72043,15 @@
         <v>6.425438596491231</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>414.6726726726727</v>
       </c>
       <c r="I48" t="n">
-        <v>414.6726726726727</v>
+        <v>4.399399399399401</v>
       </c>
       <c r="J48" t="n">
-        <v>4.399399399399401</v>
-      </c>
-      <c r="K48" t="n">
         <v>1.060933041727619</v>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -72110,18 +72084,15 @@
         <v>8.311688311688318</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>275.4444444444445</v>
       </c>
       <c r="I49" t="n">
-        <v>275.4444444444445</v>
+        <v>3.843843843843847</v>
       </c>
       <c r="J49" t="n">
-        <v>3.843843843843847</v>
-      </c>
-      <c r="K49" t="n">
         <v>1.395506034473361</v>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -72154,18 +72125,15 @@
         <v>8.181818181818175</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>254.7237237237237</v>
       </c>
       <c r="I50" t="n">
-        <v>254.7237237237237</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="J50" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="K50" t="n">
         <v>1.485446164365796</v>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -72198,18 +72166,15 @@
         <v>4.660194174757257</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>279.9481981981982</v>
       </c>
       <c r="I51" t="n">
-        <v>279.9481981981982</v>
+        <v>2.162162162162151</v>
       </c>
       <c r="J51" t="n">
-        <v>2.162162162162151</v>
-      </c>
-      <c r="K51" t="n">
         <v>0.7723436607480431</v>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -72226,7 +72191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72252,20 +72217,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -72298,9 +72258,6 @@
       <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="n">
-        <v>50</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -72321,15 +72278,12 @@
         <v>6.258444725844185</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>313.2080630630631</v>
       </c>
       <c r="G3" t="n">
-        <v>313.2080630630631</v>
+        <v>3.496396396396393</v>
       </c>
       <c r="H3" t="n">
-        <v>3.496396396396393</v>
-      </c>
-      <c r="I3" t="n">
         <v>1.070007611199766</v>
       </c>
     </row>
@@ -72352,15 +72306,12 @@
         <v>2.829767814552088</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>62.05871037211984</v>
       </c>
       <c r="G4" t="n">
-        <v>62.05871037211984</v>
+        <v>1.859406365147517</v>
       </c>
       <c r="H4" t="n">
-        <v>1.859406365147517</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.4733001450006397</v>
       </c>
     </row>
@@ -72383,15 +72334,12 @@
         <v>1.315789473684204</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>168.3205705705706</v>
       </c>
       <c r="G5" t="n">
-        <v>168.3205705705706</v>
+        <v>0.7807807807807814</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7807807807807814</v>
-      </c>
-      <c r="I5" t="n">
         <v>0.2307134078048235</v>
       </c>
     </row>
@@ -72414,15 +72362,12 @@
         <v>3.557283262432153</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>274.7698948948949</v>
       </c>
       <c r="G6" t="n">
-        <v>274.7698948948949</v>
+        <v>1.756756756756755</v>
       </c>
       <c r="H6" t="n">
-        <v>1.756756756756755</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.6227154848476959</v>
       </c>
     </row>
@@ -72445,15 +72390,12 @@
         <v>6.929287636649433</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>305.8945195195195</v>
       </c>
       <c r="G7" t="n">
-        <v>305.8945195195195</v>
+        <v>3.78378378378378</v>
       </c>
       <c r="H7" t="n">
-        <v>3.78378378378378</v>
-      </c>
-      <c r="I7" t="n">
         <v>1.173222119859653</v>
       </c>
     </row>
@@ -72476,15 +72418,12 @@
         <v>8.42606044728128</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>359.3836336336336</v>
       </c>
       <c r="G8" t="n">
-        <v>359.3836336336336</v>
+        <v>4.628378378378372</v>
       </c>
       <c r="H8" t="n">
-        <v>4.628378378378372</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.456296040266281</v>
       </c>
     </row>
@@ -72507,15 +72446,12 @@
         <v>10.00000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>432.9579579579579</v>
       </c>
       <c r="G9" t="n">
-        <v>432.9579579579579</v>
+        <v>6.936936936936946</v>
       </c>
       <c r="H9" t="n">
-        <v>6.936936936936946</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.702478912477109</v>
       </c>
     </row>
